--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -864,7 +864,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 1 progress: 66 of 105 items resolved (Done / Moved-to-Epic-3)  (63%)</t>
+          <t>Epic 1 progress: 70 of 105 items resolved (Done / Moved-to-Epic-3)  (67%)</t>
         </is>
       </c>
     </row>
@@ -946,14 +946,14 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -7221,9 +7221,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J85" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K85" s="30" t="n"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="O85" s="30" t="inlineStr">
         <is>
-          <t>LIVE-TEST EXAMPLE (2026-08-13): New Kapoor tenant clicked 'Structure it' in Decision Desk - nothing visible happened. Backend returned 451 for /api/capture/clarify. Real user would think the app is broken.</t>
+          <t>SHIPPED 2026-08-15. Axios response interceptor in frontend/src/lib/api.js. On any 451 (Unavailable For Legal Reasons -- DPDP consent gate), shows a toast with an Open Settings action that jumps to /settings#ai-consent. Debounced 8s so repeated LLM failures don't flood the bell. | Previous: LIVE-TEST EXAMPLE (2026-08-13): New Kapoor tenant clicked 'Structure it' in Decision Desk - nothing visible happened. Backend returned 451 for /api/capture/clarify. Real user would think the app is br</t>
         </is>
       </c>
     </row>
@@ -7282,9 +7282,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J86" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K86" s="30" t="n"/>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O86" s="30" t="inlineStr">
         <is>
-          <t>LIVE-TEST EXAMPLE (2026-08-13): Signed up with amit@kapoorcotton.test - blueprint generated, 'Enter DecisionOS' click silently failed. Only saw the 422 via DevTools network tab.</t>
+          <t>SHIPPED 2026-08-15. formatApiError() now unwraps FastAPI 422 nested detail (loc + msg) into readable field:message strings. BuildReveal signup review now renders errors in a prominent bordered red banner with title 'Couldn't create your workspace' instead of a small red line. Data-testid=build-error-banner for E2E. | Previous: LIVE-TEST EXAMPLE (2026-08-13): Signed up with amit@kapoorcotton.test - blueprint generated, 'Enter DecisionOS' click silently failed. Only saw the 422 via DevTools network tab.</t>
         </is>
       </c>
     </row>
@@ -8380,9 +8380,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J104" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K104" s="30" t="n"/>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="O104" s="30" t="inlineStr">
         <is>
-          <t>LIVE-TEST EXAMPLE (2026-08-13): Priya (finance) tried COMPLETE on 'Raise GST invoice for Kapoor Retail order' - two mouse clicks + one JS click, zero network activity. Only the status dropdown finished the task.</t>
+          <t>SHIPPED 2026-08-15. Killed the window.confirm() from complete(). Also removed the disabled flag on the button -- evidence check now runs inside the handler and shows a clear toast. Live-verified in browser: 13 Complete buttons on My Work all disabled=false, all title='Mark as complete'. | Previous: LIVE-TEST EXAMPLE (2026-08-13): Priya (finance) tried COMPLETE on 'Raise GST invoice for Kapoor Retail order' - two mouse clicks + one JS click, zero network activity. Only the status dropdown finishe</t>
         </is>
       </c>
     </row>
@@ -8441,9 +8441,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J105" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J105" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K105" s="30" t="n"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="O105" s="30" t="inlineStr">
         <is>
-          <t>LIVE-TEST EXAMPLE (2026-08-13): Both Kapoor + Delhi GST-invoice tasks completed; /ask still shows INVOICES=0 BILLED=Rs 0 OUTSTANDING=Rs 0. Brain's narrative: 'these invoices may not yet have been entered into the finance/accounting module... this is a data gap.' Composes with WE-06 side-effects framework.</t>
+          <t>SHIPPED 2026-08-15. New _maybe_auto_invoice hook in routers/tasks.py fires on task PATCH to status=done. Trigger: title matches invoice keyword AND task has contact_id OR amount. Adds a sales_invoice with status=draft, source=auto_from_task, source_task_id for dedup, contact name resolved from contacts. TaskCreateInput extended with contact_id + contact_name + amount so finance metadata carries forward. Live E2E: created task 'Raise GST invoice for Delhi Retail order' with amount=50000 -&gt; mark done -&gt; invoice draft appeared with contact_name=Delhi Retail Corp, amount=50000, status=draft. Kills the INVOICES=0 cash-flow blind spot the Brain narrated. | Previous: LIVE-TEST EXAMPLE (2026-08-13): Both Kapoor + Delhi GST-invoice tasks completed; /ask still shows INVOICES=0 BILLED=Rs 0 OUTSTANDING=Rs 0. Brain's narrative: 'these invoices may not yet have been ente</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -864,7 +864,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 1 progress: 70 of 105 items resolved (Done / Moved-to-Epic-3)  (67%)</t>
+          <t>Epic 1 progress: 93 of 105 items resolved (Done / Moved-to-Epic-3/5/6)  (89%)</t>
         </is>
       </c>
     </row>
@@ -1091,14 +1091,14 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>17</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1120,14 +1120,14 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>11</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1149,14 +1149,14 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>16</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -6344,9 +6344,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J72" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 6</t>
         </is>
       </c>
       <c r="K72" s="30" t="n"/>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O72" s="30" t="inlineStr">
         <is>
-          <t>Depends on RBAC-13</t>
+          <t>MOVED 2026-08-16 to Epic 6 (Enterprise RBAC) -- see DecisionOS_Epic6_Enterprise_RBAC.xlsx. Depends on RBAC-13</t>
         </is>
       </c>
     </row>
@@ -6409,9 +6409,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J73" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J73" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 6</t>
         </is>
       </c>
       <c r="K73" s="30" t="n"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="O73" s="30" t="inlineStr">
         <is>
-          <t>Depends on RBAC-13</t>
+          <t>MOVED 2026-08-16 to Epic 6 (Enterprise RBAC) -- see DecisionOS_Epic6_Enterprise_RBAC.xlsx. Depends on RBAC-13</t>
         </is>
       </c>
     </row>
@@ -6912,9 +6912,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J80" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K80" s="30" t="n"/>
@@ -6925,7 +6925,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O80" s="30" t="n"/>
+      <c r="O80" s="30" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-16. New routers/access.py POST/DELETE/GET /me/acting-as. Delegate stored on user.acting_as, active-now check based on from/to window. Approver-routing sites read via resolve_delegate(). Live E2E: set Rahul Mehta as delegate 2026-08-15 -&gt; 2026-08-22 -&gt; GET returned active_now=True, cleared, gone.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="30" t="inlineStr">
@@ -6973,9 +6977,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J81" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K81" s="30" t="n"/>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="O81" s="30" t="inlineStr">
         <is>
-          <t>Depends on RBAC-13</t>
+          <t>SHIPPED 2026-08-16. New routers/access.py POST /users/{uid}/temp-grant + DELETE + GET. Grants stored on membership.temp_grants[]. user_perms() merges non-expired grants. run_followup scheduler sweeps expired grants + writes audit entry. Live E2E: granted 'finance' to Sonia (sales) until 2026-09-15 -&gt; GET returned 1 active grant -&gt; revoked -&gt; 200.</t>
         </is>
       </c>
     </row>
@@ -7038,9 +7042,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="J82" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J82" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 6</t>
         </is>
       </c>
       <c r="K82" s="30" t="n"/>
@@ -7053,7 +7057,7 @@
       </c>
       <c r="O82" s="30" t="inlineStr">
         <is>
-          <t>Depends on RBAC-12</t>
+          <t>MOVED 2026-08-16 to Epic 6 (Enterprise RBAC) -- see DecisionOS_Epic6_Enterprise_RBAC.xlsx. Depends on RBAC-12</t>
         </is>
       </c>
     </row>
@@ -7103,9 +7107,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J83" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J83" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 6</t>
         </is>
       </c>
       <c r="K83" s="30" t="n"/>
@@ -7116,7 +7120,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O83" s="30" t="n"/>
+      <c r="O83" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOVED 2026-08-16 to Epic 6 (Enterprise RBAC) -- see DecisionOS_Epic6_Enterprise_RBAC.xlsx. </t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="30" t="inlineStr">
@@ -7164,9 +7172,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="J84" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J84" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 6</t>
         </is>
       </c>
       <c r="K84" s="30" t="n"/>
@@ -7177,7 +7185,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O84" s="30" t="n"/>
+      <c r="O84" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOVED 2026-08-16 to Epic 6 (Enterprise RBAC) -- see DecisionOS_Epic6_Enterprise_RBAC.xlsx. </t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="30" t="inlineStr">
@@ -7404,9 +7416,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J88" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J88" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K88" s="30" t="n"/>
@@ -7419,7 +7431,7 @@
       </c>
       <c r="O88" s="30" t="inlineStr">
         <is>
-          <t>Foundational — unlocks WE-06..WE-09 (the engine needs to read these). See Spec deck slide 9 (data model table).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Foundational — unlocks WE-06..WE-09 (the engine needs to read these). See Spec deck slide 9 (data model table).</t>
         </is>
       </c>
     </row>
@@ -7465,9 +7477,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J89" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J89" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K89" s="30" t="n"/>
@@ -7480,7 +7492,7 @@
       </c>
       <c r="O89" s="30" t="inlineStr">
         <is>
-          <t>Enables WE-04 Settings redesign. Idempotent via migration ledger.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Enables WE-04 Settings redesign. Idempotent via migration ledger.</t>
         </is>
       </c>
     </row>
@@ -7526,9 +7538,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J90" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J90" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K90" s="30" t="n"/>
@@ -7541,7 +7553,7 @@
       </c>
       <c r="O90" s="30" t="inlineStr">
         <is>
-          <t>The single most important schema change of the sprint — everything downstream (engine, side-effects, joined UI) reads this shape.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. The single most important schema change of the sprint — everything downstream (engine, side-effects, joined UI) reads this shape.</t>
         </is>
       </c>
     </row>
@@ -7587,9 +7599,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J91" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J91" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K91" s="30" t="n"/>
@@ -7602,7 +7614,7 @@
       </c>
       <c r="O91" s="30" t="inlineStr">
         <is>
-          <t>Depends on WE-03 (stage-object shape). See Spec deck slide 12.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Depends on WE-03 (stage-object shape). See Spec deck slide 12.</t>
         </is>
       </c>
     </row>
@@ -7648,9 +7660,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J92" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J92" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K92" s="30" t="n"/>
@@ -7663,7 +7675,7 @@
       </c>
       <c r="O92" s="30" t="inlineStr">
         <is>
-          <t>See Testing Plan deck slide 4 (Phase 1 exit gate).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. See Testing Plan deck slide 4 (Phase 1 exit gate).</t>
         </is>
       </c>
     </row>
@@ -7709,9 +7721,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="J93" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J93" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K93" s="30" t="n"/>
@@ -7724,7 +7736,7 @@
       </c>
       <c r="O93" s="30" t="inlineStr">
         <is>
-          <t>The core of the sprint. See Spec deck slide 10 (function table).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. The core of the sprint. See Spec deck slide 10 (function table).</t>
         </is>
       </c>
     </row>
@@ -7770,9 +7782,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J94" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J94" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K94" s="30" t="n"/>
@@ -7785,7 +7797,7 @@
       </c>
       <c r="O94" s="30" t="inlineStr">
         <is>
-          <t>Prevents regression forever — future refactors that add a stray workflows.update_one({stage:...}) fail the contract test at CI.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Prevents regression forever — future refactors that add a stray workflows.update_one({stage:...}) fail the contract test at CI.</t>
         </is>
       </c>
     </row>
@@ -7831,9 +7843,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J95" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J95" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K95" s="30" t="n"/>
@@ -7846,7 +7858,7 @@
       </c>
       <c r="O95" s="30" t="inlineStr">
         <is>
-          <t>Migrates the FIX-001-B pattern from bespoke advance_workflow code into a first-class engine capability. Every future 'when stage X, do Y' request lands here without touching the router.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Migrates the FIX-001-B pattern from bespoke advance_workflow code into a first-class engine capability. Every future 'when stage X, do Y' request lands here without touching the router.</t>
         </is>
       </c>
     </row>
@@ -7892,9 +7904,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J96" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J96" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K96" s="30" t="n"/>
@@ -7907,7 +7919,7 @@
       </c>
       <c r="O96" s="30" t="inlineStr">
         <is>
-          <t>Prevents the two hardest-to-diagnose classes of workflow bugs. Regression tests in Testing Plan deck slide 6.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Prevents the two hardest-to-diagnose classes of workflow bugs. Regression tests in Testing Plan deck slide 6.</t>
         </is>
       </c>
     </row>
@@ -7953,9 +7965,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J97" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J97" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K97" s="30" t="n"/>
@@ -7968,7 +7980,7 @@
       </c>
       <c r="O97" s="30" t="inlineStr">
         <is>
-          <t>See Testing Plan deck slides 5-7 (Phase 2 core + guarantees + stage-object migration).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. See Testing Plan deck slides 5-7 (Phase 2 core + guarantees + stage-object migration).</t>
         </is>
       </c>
     </row>
@@ -8014,9 +8026,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J98" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J98" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K98" s="30" t="n"/>
@@ -8029,7 +8041,7 @@
       </c>
       <c r="O98" s="30" t="inlineStr">
         <is>
-          <t>See Spec deck slide 13 (My Work + Workflow, joined).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. See Spec deck slide 13 (My Work + Workflow, joined).</t>
         </is>
       </c>
     </row>
@@ -8075,9 +8087,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J99" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J99" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K99" s="30" t="n"/>
@@ -8090,7 +8102,7 @@
       </c>
       <c r="O99" s="30" t="inlineStr">
         <is>
-          <t>The other half of WE-11 — from the workflow-board side.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. The other half of WE-11 — from the workflow-board side.</t>
         </is>
       </c>
     </row>
@@ -8136,9 +8148,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J100" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J100" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K100" s="30" t="n"/>
@@ -8151,7 +8163,7 @@
       </c>
       <c r="O100" s="30" t="inlineStr">
         <is>
-          <t>Pairs with WE-07 (single-writer contract). The override IS allowed — but never invisible.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Pairs with WE-07 (single-writer contract). The override IS allowed — but never invisible.</t>
         </is>
       </c>
     </row>
@@ -8197,9 +8209,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="J101" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J101" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K101" s="30" t="n"/>
@@ -8212,7 +8224,7 @@
       </c>
       <c r="O101" s="30" t="inlineStr">
         <is>
-          <t>Trivial cleanup — but leaving it in would confuse users about which surface is authoritative.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. Trivial cleanup — but leaving it in would confuse users about which surface is authoritative.</t>
         </is>
       </c>
     </row>
@@ -8258,9 +8270,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J102" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J102" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K102" s="30" t="n"/>
@@ -8273,7 +8285,7 @@
       </c>
       <c r="O102" s="30" t="inlineStr">
         <is>
-          <t>This is THE test that proves the sprint delivered. See Testing Plan deck slide 9 (Kapoor golden path). Adds ~15-20 assertions.</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. This is THE test that proves the sprint delivered. See Testing Plan deck slide 9 (Kapoor golden path). Adds ~15-20 assertions.</t>
         </is>
       </c>
     </row>
@@ -8319,9 +8331,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J103" s="30" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J103" s="28" t="inlineStr">
+        <is>
+          <t>Moved to Epic 5</t>
         </is>
       </c>
       <c r="K103" s="30" t="n"/>
@@ -8334,7 +8346,7 @@
       </c>
       <c r="O103" s="30" t="inlineStr">
         <is>
-          <t>See Testing Plan deck slide 10 (regression + back-compat) and slide 11 (per-phase exit gates).</t>
+          <t>MOVED 2026-08-16 to Epic 5 (Workflow Engine) -- see DecisionOS_Epic5_Workflow_Engine.xlsx. See Testing Plan deck slide 10 (regression + back-compat) and slide 11 (per-phase exit gates).</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -864,7 +864,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 1 progress: 93 of 105 items resolved (Done / Moved-to-Epic-3/5/6)  (89%)</t>
+          <t>Epic 1 progress: 94 of 105 items resolved  (90%)</t>
         </is>
       </c>
     </row>
@@ -1062,14 +1062,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -3454,9 +3454,9 @@
           <t>L</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K30" s="17" t="n"/>
@@ -3467,7 +3467,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O30" s="17" t="n"/>
+      <c r="O30" s="17" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-16. Backend module only per founder ask (redirect-to-landing pattern). See commit message for endpoint contracts.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="17" t="inlineStr">

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -342,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -468,6 +468,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -884,10 +890,8 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -932,7 +936,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -990,7 +996,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1019,7 +1027,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1048,7 +1058,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -1271,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8534,6 +8546,314 @@
       <c r="O106" s="30" t="inlineStr">
         <is>
           <t>SHIPPED 2026-08-13 in FIX-FUP-51. Live-verified: priya (finance) blocked at nav + route + API. amit (owner) sees 3 seeded suppliers. Backend + frontend mirror both updated. 23/23 RBAC gates tests pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="45" t="inlineStr">
+        <is>
+          <t>S5-AUDIT-01</t>
+        </is>
+      </c>
+      <c r="B107" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C107" s="45" t="inlineStr">
+        <is>
+          <t>DB/Indexes</t>
+        </is>
+      </c>
+      <c r="D107" s="45" t="inlineStr">
+        <is>
+          <t>Add missing indexes: billing_events + crm_activities + invoices</t>
+        </is>
+      </c>
+      <c r="E107" s="45" t="inlineStr">
+        <is>
+          <t>Unique idx on billing_events.idempotency_key (Razorpay webhook idempotency). Compound (tenant_id, contact_id, created_at desc) on crm_activities. Partial idx on invoices.source_task_id.</t>
+        </is>
+      </c>
+      <c r="F107" s="45" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G107" s="45" t="inlineStr">
+        <is>
+          <t>Pre-migration audit 2026-08-16</t>
+        </is>
+      </c>
+      <c r="H107" s="45" t="inlineStr">
+        <is>
+          <t>backend/server.py::_bootstrap</t>
+        </is>
+      </c>
+      <c r="I107" s="45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K107" s="45" t="inlineStr">
+        <is>
+          <t>kishan</t>
+        </is>
+      </c>
+      <c r="L107" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M107" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="N107" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O107" s="45" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-16. Verified indexes materialised in MongoDB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="46" t="inlineStr">
+        <is>
+          <t>S5-AUDIT-02</t>
+        </is>
+      </c>
+      <c r="B108" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C108" s="46" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D108" s="46" t="inlineStr">
+        <is>
+          <t>Razorpay webhook: catch DuplicateKeyError under race</t>
+        </is>
+      </c>
+      <c r="E108" s="46" t="inlineStr">
+        <is>
+          <t>Belt (unique index on idempotency_key) + braces (catch DuplicateKeyError in handler). Race between find_one and insert_one no longer double-processes.</t>
+        </is>
+      </c>
+      <c r="F108" s="46" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G108" s="46" t="inlineStr">
+        <is>
+          <t>Pre-migration audit 2026-08-16</t>
+        </is>
+      </c>
+      <c r="H108" s="46" t="inlineStr">
+        <is>
+          <t>backend/routers/billing.py::razorpay_webhook</t>
+        </is>
+      </c>
+      <c r="I108" s="46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K108" s="46" t="inlineStr">
+        <is>
+          <t>kishan</t>
+        </is>
+      </c>
+      <c r="L108" s="46" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M108" s="46" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="N108" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O108" s="46" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-16 with S5-AUDIT-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>S5-AUDIT-03</t>
+        </is>
+      </c>
+      <c r="B109" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C109" s="45" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="D109" s="45" t="inlineStr">
+        <is>
+          <t>WhatsApp webhook: guard message['text'] KeyError</t>
+        </is>
+      </c>
+      <c r="E109" s="45" t="inlineStr">
+        <is>
+          <t>Use ((message.get('text') or {}).get('body') or '').strip() and return ignored on empty. Prevents public 500 for image/audio/reaction inbound messages that lack text.body.</t>
+        </is>
+      </c>
+      <c r="F109" s="45" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G109" s="45" t="inlineStr">
+        <is>
+          <t>Pre-migration audit 2026-08-16</t>
+        </is>
+      </c>
+      <c r="H109" s="45" t="inlineStr">
+        <is>
+          <t>backend/server.py:5283</t>
+        </is>
+      </c>
+      <c r="I109" s="45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K109" s="45" t="inlineStr">
+        <is>
+          <t>kishan</t>
+        </is>
+      </c>
+      <c r="L109" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M109" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="N109" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O109" s="45" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-16. Meta was retrying webhook -&gt; sentry noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="46" t="inlineStr">
+        <is>
+          <t>S5-AUDIT-04</t>
+        </is>
+      </c>
+      <c r="B110" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C110" s="46" t="inlineStr">
+        <is>
+          <t>Observability</t>
+        </is>
+      </c>
+      <c r="D110" s="46" t="inlineStr">
+        <is>
+          <t>Migration swallows: logger.warning -&gt; logger.exception (9 sites)</t>
+        </is>
+      </c>
+      <c r="E110" s="46" t="inlineStr">
+        <is>
+          <t>All 9 try/except migration blocks in server.py _bootstrap upgraded to logger.exception so silent failures leave tracebacks. Also hoisted _apply_migration import to function top (was below callsites, UnboundLocalError swallowed).</t>
+        </is>
+      </c>
+      <c r="F110" s="46" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G110" s="46" t="inlineStr">
+        <is>
+          <t>Pre-migration audit 2026-08-16</t>
+        </is>
+      </c>
+      <c r="H110" s="46" t="inlineStr">
+        <is>
+          <t>backend/server.py:6123,6268,6298,6345,6437,6489,6538,6573,6715,6728</t>
+        </is>
+      </c>
+      <c r="I110" s="46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K110" s="46" t="inlineStr">
+        <is>
+          <t>kishan</t>
+        </is>
+      </c>
+      <c r="L110" s="46" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M110" s="46" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="N110" s="46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O110" s="46" t="inlineStr">
+        <is>
+          <t>3 migrations had been silently failing for weeks (backfill_memberships, backfill_grandfathered_plans, rename_production_role) -&gt; real prod drift caught by audit.</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -874,6 +874,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -964,7 +965,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -1086,7 +1087,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
@@ -1173,7 +1174,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr"/>

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -870,7 +870,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 1 progress: 94 of 105 items resolved  (90%)</t>
+          <t>Epic 1 progress: 95 of 105 items resolved  (90%)</t>
         </is>
       </c>
     </row>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>17</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr"/>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K40" s="17" t="n"/>
@@ -4186,7 +4186,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O40" s="17" t="n"/>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-08-27: brain.py compute handlers already used a central _COMPUTE_HANDLERS dict registry; formalized the 4 brain_router.py agent tools the same way (_TOOL_HANDLERS registry + adapter, replacing the if/elif dispatch). Add a tool = define _tool_&lt;name&gt; + one registry line. Pydantic in/out wrapping deliberately skipped -- these are internal handlers with consistent (ctx,plan,recs)/(t,user) contracts; Pydantic ceremony adds no value off the API boundary.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="17" t="inlineStr">

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -874,7 +874,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -21195,7 +21194,7 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>Testing Plan</t>
+          <t>Epic 10 (Testing) -- AUTOMATED dimensions S1-S12 GREEN: unit/functional/RBAC/onboarding/multi-niche/team-scale/formula/isolation/AI-extraction/concurrency/regression + S12 E2E persona journeys (owner/finance/sales/ops + WhatsApp + voice + Kapoor golden path) + exit gate (test_s12_exit_gate.py). STILL PENDING (manual/ops, Epic 1 S5): phase D load/perf, phase F backup-DR &amp; migration dry-run, phases G-J internal-alpha/closed-beta/staged-beta/GA. Flip to TRUE only when those land.</t>
         </is>
       </c>
       <c r="D24" s="37" t="inlineStr">

--- a/docs/DecisionOS_Epic1_Stability.xlsx
+++ b/docs/DecisionOS_Epic1_Stability.xlsx
@@ -856,7 +856,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DecisionOS - Epic 1 - Stability, Security, RBAC</t>
+          <t>Epic 1 -- Stability/Security/RBAC. Sprints 0-3 + 2.5 COMPLETE. Sprint 5 (go-live) engineering DONE: observability (Sentry+JSON logs+request-id), CI/CD (test-gate + deploy pipeline), idempotent migration + pre-deploy verify, backup/restore runbook + PASSED restore drill, rollback + staged-rollout runbooks. Remaining 4 are pure infra/ops (staging env, load-test run, secrets rotation, final go/no-go) -- need a real environment + human sign-off, not code. See docs/runbooks/.</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O45" s="17" t="n"/>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>BLOCKED (infra). Needs a real staging environment stood up on the deploy platform -- cannot be created from code. Everything downstream (S5-02 load test, rollback rehearsal) targets it. Founder/ops step.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
@@ -4587,7 +4591,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O46" s="17" t="n"/>
+      <c r="O46" s="17" t="inlineStr">
+        <is>
+          <t>ARTIFACT READY, run pending infra. k6 script ops/loadtest/loadtest.k6.js -- 100-tenant dashboard+capture mix, morning burst, SLO thresholds (p95&lt;500ms read / &lt;1.5s capture, err&lt;1%). Run against staging (S5-01): `BASE_URL=... k6 run --vus 100 --duration 5m ...`. Ops step.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
@@ -4637,7 +4645,7 @@
       </c>
       <c r="J47" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K47" s="17" t="n"/>
@@ -4648,7 +4656,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O47" s="17" t="n"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. Observability shipped: core/observability.py -- opt-in Sentry error+perf tracking (SENTRY_DSN, import-guarded, no PII), structured JSON logs (LOG_FORMAT=json), and X-Request-ID correlation on every request; wired in server.py; sentry-sdk added to requirements. No-op unless configured. See docs/runbooks/OBSERVABILITY.md. (Activating in prod = set the env vars.)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
@@ -4698,7 +4710,7 @@
       </c>
       <c r="J48" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K48" s="17" t="n"/>
@@ -4709,7 +4721,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O48" s="17" t="n"/>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. Backup/restore runbook (docs/runbooks/BACKUP_RESTORE.md, RPO/RTO defined) + scripts/restore_drill.py, and the drill was RUN + PASSED -- real round-trip of 148 docs across 6 collections into a throwaway DB, counts verified, dropped (RTO ~10s). Prod: enable managed daily snapshots + PITR.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
@@ -4759,7 +4775,7 @@
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K49" s="17" t="n"/>
@@ -4770,7 +4786,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O49" s="17" t="n"/>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. Migration is idempotent + additive, applied at boot via bootstrap._bootstrap; scripts/migrate.py runs it standalone as a pre-deploy verify step (in deploy.yml, gated on tests). Inventory + freeze/verify procedure in docs/runbooks/MIGRATION_PLAN.md.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
@@ -4820,7 +4840,7 @@
       </c>
       <c r="J50" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K50" s="17" t="n"/>
@@ -4831,7 +4851,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O50" s="17" t="n"/>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. CI existed (.github/workflows/tests.yml: unit gate + db + integration). Added CD pipeline ops/ci/deploy.yml (install to .github/workflows/ -- the CI token lacks GitHub 'workflow' scope): test gate -&gt; migrate (schema verify) -&gt; deploy staging -&gt; deploy production (manual-approval env). No more manual deploys; wire RAILWAY_TOKEN + secrets per docs/runbooks/SECRETS.md.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="17" t="inlineStr">
@@ -4881,7 +4905,7 @@
       </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K51" s="17" t="n"/>
@@ -4892,7 +4916,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O51" s="17" t="n"/>
+      <c r="O51" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. Rollback procedure written (docs/runbooks/ROLLBACK.md): &lt;10min revert via platform one-click or git revert; schema is forward-safe (additive/idempotent) so no schema downgrade; verify steps + guardrails (test gate, staged rollout, graceful shutdown). Rehearse on staging.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
@@ -4953,7 +4981,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O52" s="17" t="n"/>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>PARTIAL. Verified the 'never in image/git' half: .env git-ignored (.gitignore) + excluded from the image (.dockerignore) + not tracked. Rotation procedure + secrets inventory in docs/runbooks/SECRETS.md. LIVE rotation into the platform vault is the ops step (rotate creds/keys, add GitHub Actions secrets).</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="17" t="inlineStr">
@@ -5003,7 +5035,7 @@
       </c>
       <c r="J53" s="26" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K53" s="17" t="n"/>
@@ -5014,7 +5046,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O53" s="17" t="n"/>
+      <c r="O53" s="17" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-02. Staged rollout plan (docs/runbooks/STAGED_ROLLOUT.md): alpha-&gt;closed-beta-&gt;5/20/50-&gt;GA with per-tier SLO exit bars + checkpoint dashboard + abort criteria; ENFORCED in deploy.yml via a production Environment required-reviewer gate between staging and prod.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
@@ -5075,7 +5111,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O54" s="17" t="n"/>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>PARTIAL. Go/no-go checklist + current-state assessment written (docs/runbooks/GO_LIVE_GO_NO_GO.md): engineering+docs = Go; the No-Go items are all infra/ops (staging, load-test run, secrets rotation, Sentry activation). The final review HELD WITH THE TEAM is the human step before launch.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="30" t="inlineStr">
@@ -20798,7 +20838,7 @@
       </c>
       <c r="C6" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>.env verified out of image/git; rotation procedure in SECRETS.md (ops)</t>
         </is>
       </c>
       <c r="D6" s="37" t="inlineStr">
@@ -21040,7 +21080,7 @@
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>infra to provision (S5-01); STAGED_ROLLOUT.md</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
@@ -21062,7 +21102,7 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>k6 script ready (ops/loadtest); run on staging (S5-02)</t>
         </is>
       </c>
       <c r="D18" s="37" t="inlineStr">
@@ -21084,7 +21124,7 @@
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>integration shipped (core/observability.py + OBSERVABILITY.md); set SENTRY_DSN in prod to activate</t>
         </is>
       </c>
       <c r="D19" s="37" t="inlineStr">
@@ -21106,12 +21146,12 @@
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>restore-drill PASSED (backend/scripts/restore_drill.py) + BACKUP_RESTORE.md; enable managed prod snapshots</t>
         </is>
       </c>
       <c r="D20" s="37" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -21128,12 +21168,12 @@
       </c>
       <c r="C21" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>idempotent bootstrap + scripts/migrate.py in deploy.yml; MIGRATION_PLAN.md</t>
         </is>
       </c>
       <c r="D21" s="37" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -21150,7 +21190,7 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>procedure written (ROLLBACK.md); rehearse on staging</t>
         </is>
       </c>
       <c r="D22" s="37" t="inlineStr">
@@ -21172,12 +21212,12 @@
       </c>
       <c r="C23" s="38" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>plan written + enforced via deploy.yml env approvals (STAGED_ROLLOUT.md)</t>
         </is>
       </c>
       <c r="D23" s="37" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
